--- a/plantillas/42.xlsx
+++ b/plantillas/42.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$6</definedName>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/42.xlsx
+++ b/plantillas/42.xlsx
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/42.xlsx
+++ b/plantillas/42.xlsx
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
